--- a/游戏设计王/老虎机数学入门-PartVI-独立滚轮老虎机.xlsx
+++ b/游戏设计王/老虎机数学入门-PartVI-独立滚轮老虎机.xlsx
@@ -404,12 +404,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="5">
+  <numFmts count="6">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="0.000%"/>
+    <numFmt numFmtId="177" formatCode="0.0000000000%"/>
   </numFmts>
   <fonts count="33">
     <font>
@@ -1114,7 +1115,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1199,6 +1200,8 @@
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="177" applyNumberFormat="1" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="177" applyNumberFormat="1" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -4981,7 +4984,7 @@
       <c r="A28" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="B28" s="9">
+      <c r="B28" s="42">
         <f>((B$5*C$5*D$5)*B17+(B$6*C$6*D$6)*B18+(B$7*C$7*D$7)*B19+(B$8*C$8*D$8)*B20+(B$9*C$9*D$9)*B21)/(B$10*C$10*D$10)</f>
         <v>0.576</v>
       </c>
@@ -5014,7 +5017,7 @@
       <c r="A29" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="B29" s="9">
+      <c r="B29" s="42">
         <f>((E$5*F$5*G$5)*B17+(E$6*F$6*G$6)*B18+(E$7*F$7*G$7)*B19+(E$8*F$8*G$8)*B20+(E$9*F$9*G$9)*B21)/(E$10*F$10*G$10)</f>
         <v>0.576</v>
       </c>
@@ -5047,7 +5050,7 @@
       <c r="A30" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="B30" s="9">
+      <c r="B30" s="42">
         <f>((H$5*I$5*J$5)*B17+(H$6*I$6*J$6)*B18+(H$7*I$7*J$7)*B19+(H$8*I$8*J$8)*B20+(H$9*I$9*J$9)*B21)/(H$10*I$10*J$10)</f>
         <v>0.762</v>
       </c>
@@ -5080,7 +5083,7 @@
       <c r="A31" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="B31" s="9">
+      <c r="B31" s="42">
         <f>((B$5*F$5*J$5)*B17+(B$6*F$6*J$6)*B18+(B$7*F$7*J$7)*B19+(B$8*F$8*J$8)*B20+(B$9*F$9*J$9)*B21)/(B$10*F$10*J$10)</f>
         <v>0.762</v>
       </c>
@@ -5113,7 +5116,7 @@
       <c r="A32" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="B32" s="9">
+      <c r="B32" s="42">
         <f>((H$5*F$5*D$5)*B17+(H$6*F$6*D$6)*B18+(H$7*F$7*D$7)*B19+(H$8*F$8*D$8)*B20+(H$9*F$9*D$9)*B21)/(H$10*F$10*D$10)</f>
         <v>0.576</v>
       </c>
@@ -5178,7 +5181,7 @@
       <c r="A34" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="B34" s="10">
+      <c r="B34" s="43">
         <f>AVERAGE(B28:B32)</f>
         <v>0.6504</v>
       </c>
